--- a/tmp_save/npu_model_dataset_paths.xlsx
+++ b/tmp_save/npu_model_dataset_paths.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pllimax\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pllimax\WPSDrive\1877599402\WPS云盘\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="113">
   <si>
     <t>类型</t>
   </si>
@@ -49,6 +49,9 @@
     <t>使用用例</t>
   </si>
   <si>
+    <t>使用runner</t>
+  </si>
+  <si>
     <t>模型权重</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
     <t>test/registered/npu/accuracy/deepseek_v4_flash/test_npu_deepseek_v4_flash_w8a8_8p_gpqa.py; test/registered/npu/performance/deepseek_v4_flash/test_npu_deepseek_v4_flash_w8a8_1p1d_16p_in8k_out1k_50ms.py; test/registered/npu/performance/deepseek_v4_flash/test_npu_deepseek_v4_flash_w8a8_8p_in32k_out1k_50ms.py; test/registered/npu/performance/deepseek_v4_flash/test_npu_deepseek_v4_flash_w8a8_8p_in8k_out1k_50ms.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-16- | linux-aarch64-a3-800t-16 | linux-amd64-cpu-4 (头节点, NPU 节点由脚本动态分配)</t>
+  </si>
+  <si>
     <t>280G</t>
   </si>
   <si>
@@ -76,6 +82,9 @@
     <t>test/registered/npu/accuracy/glm5_1/test_npu_glm5_1_w4a8_1p1d_32p_in64k_out1k_50ms_aime26.py; test/registered/npu/performance/glm5_1/test_npu_glm5_1_w4a8_1p1d_32p_in64k_out1k_50ms.py</t>
   </si>
   <si>
+    <t>linux-amd64-cpu-4 (头节点, NPU 节点由脚本动态分配)</t>
+  </si>
+  <si>
     <t>378G</t>
   </si>
   <si>
@@ -94,6 +103,9 @@
     <t>test/registered/npu/basic_function/quant/test_npu_w4a4_quantization.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-4-</t>
+  </si>
+  <si>
     <t>220G</t>
   </si>
   <si>
@@ -103,6 +115,9 @@
     <t>test/registered/npu/performance/qwen3_5_397b/test_npu_qwen3_5_397b_w4a8_8p_in3k5_out1k5_50ms.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-800t-16</t>
+  </si>
+  <si>
     <t>34G</t>
   </si>
   <si>
@@ -112,6 +127,9 @@
     <t>test/registered/npu/accuracy/qwen3_6_27b/test_npu_qwen3_6_27b_w8a8_1p_in3k5_out1k5_50ms_gpqa.py; test/registered/npu/performance/qwen3_6_27b/test_npu_qwen3_6_27b_w8a8_1p_in3k5_out1k5_50ms.py; test/registered/npu/performance/qwen3_6_27b/test_npu_qwen3_6_27b_w8a8_1p_in64k_out1k_50ms.py; test/registered/npu/performance/qwen3_6_27b/test_npu_qwen3_6_27b_w8a8_2p_in128k_out1k_50ms.py; test/registered/npu/performance/qwen3_6_27b/test_npu_qwen3_6_27b_w8a8_2p_in16k_out1k_50ms.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-2- | linux-aarch64-a3-800t-2 | linux-aarch64-a3-800t-4</t>
+  </si>
+  <si>
     <t>16G</t>
   </si>
   <si>
@@ -121,6 +139,9 @@
     <t>test/registered/npu/basic_function/quant/test_npu_autoround_moe.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-2-</t>
+  </si>
+  <si>
     <t>5.7G</t>
   </si>
   <si>
@@ -154,6 +175,9 @@
     <t>test/registered/npu/basic_function/parallel_strategy/data_parallelism/test_npu_load_balance_method_pd_disaggregation.py; test/registered/npu/basic_function/parallel_strategy/expert_parallelism/test_npu_expert_distribution_recorder_mode.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-16- | linux-aarch64-a3-2-</t>
+  </si>
+  <si>
     <t>30G</t>
   </si>
   <si>
@@ -163,6 +187,9 @@
     <t>test/registered/npu/basic_function/parallel_strategy/expert_parallelism/test_npu_eplb_min_rebalancing_utilization_threshold.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-8-</t>
+  </si>
+  <si>
     <t>62G</t>
   </si>
   <si>
@@ -172,6 +199,9 @@
     <t>test/registered/npu/basic_function/dp_attn/test_npu_dp_attention.py; test/registered/npu/basic_function/pd_disaggregation/test_npu_pd_disaggregation.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-16- | linux-aarch64-a3-4-</t>
+  </si>
+  <si>
     <t>/root/.cache/modelscope/hub/models/Qwen/Qwen3-8B</t>
   </si>
   <si>
@@ -202,6 +232,9 @@
     <t>test/registered/npu/accuracy/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_aime26.py; test/registered/npu/accuracy/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in64k_out1k_prefix90_50ms_aime26.py; test/registered/npu/performance/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in128k_out1k_50ms.py; test/registered/npu/performance/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in128k_out1k_prefix90_50ms.py; test/registered/npu/performance/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in3k5_out1k5_50ms.py; test/registered/npu/performance/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in64k_out1k_50ms.py; test/registered/npu/performance/qwen3_6_35b_a3b/test_npu_qwen3_6_35b_a3b_1p_in64k_out1k_prefix90_50ms.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-2- | linux-aarch64-a3-800t-2</t>
+  </si>
+  <si>
     <t>4.2G</t>
   </si>
   <si>
@@ -247,6 +280,9 @@
     <t>test/registered/npu/basic_function/dllm/test_npu_llada2_mini.py; test/registered/npu/basic_function/dllm/test_npu_llada2_mini_fdfo.py</t>
   </si>
   <si>
+    <t>linux-aarch64-a3-2- | linux-aarch64-a3-4-</t>
+  </si>
+  <si>
     <t>/root/.cache/modelscope/hub/models/moonshotai/Kimi-VL-A3B-Instruct</t>
   </si>
   <si>
@@ -272,6 +308,9 @@
   </si>
   <si>
     <t>test/registered/npu/basic_function/parallel_strategy/data_parallelism/test_npu_load_balance_method.py; test/registered/npu/basic_function/speculative_inference/test_npu_speculative_moe_a2a_backend.py</t>
+  </si>
+  <si>
+    <t>linux-aarch64-a3-16-</t>
   </si>
   <si>
     <t>17G</t>
@@ -947,14 +986,23 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
@@ -1499,740 +1547,803 @@
     <col min="1" max="1" width="33.875" customWidth="1"/>
     <col min="2" max="2" width="5.375" customWidth="1"/>
     <col min="3" max="3" width="110.375" customWidth="1"/>
+    <col min="5" max="5" width="9" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="107.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="4">
+        <v>4</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="2">
         <v>5</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="E8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="2">
         <v>7</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2">
+        <v>2</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="2">
+        <v>2</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="2">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="2">
+        <v>2</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="2">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1" t="s">
+      <c r="E18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D19" s="2">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="2">
+        <v>1</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="2">
+        <v>1</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" s="2">
+        <v>2</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D24" s="2">
+        <v>1</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D25" s="2">
+        <v>2</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D26" s="2">
+        <v>1</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D27" s="2">
+        <v>1</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D28" s="2">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="2">
+        <v>2</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="2">
+        <v>4</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" s="2">
+        <v>3</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="2">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="1">
+      <c r="E33" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="2">
         <v>2</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="E34" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D35" s="2">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="E35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D36" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="1">
-        <v>5</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="1">
-        <v>7</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="E36" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="2">
         <v>2</v>
       </c>
-      <c r="E13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="1">
-        <v>2</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1">
-        <v>2</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="1">
-        <v>4</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D19" s="1">
-        <v>7</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="1">
-        <v>2</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="1">
-        <v>4</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="1">
-        <v>3</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D33" s="1">
-        <v>5</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D34" s="1">
-        <v>2</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:8">
-      <c r="A36" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="A37" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="D37" s="1">
-        <v>2</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
+      <c r="E37" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="D2:D3"/>
     <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
